--- a/Planilhas_importação/Importacao_unidades.xlsx
+++ b/Planilhas_importação/Importacao_unidades.xlsx
@@ -351,25 +351,7 @@
     <t xml:space="preserve">unidade_fracao_ideal</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Liberation Serif;Times New Roman"/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">unidade_</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Liberation Serif;Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">georreferenciamento</t>
-    </r>
+    <t xml:space="preserve">unidade_georreferenciamento</t>
   </si>
   <si>
     <t xml:space="preserve">unidade_observacao</t>
@@ -385,8 +367,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="[$R$-416]\ #,##0.00;[RED]\-[$R$-416]\ #,##0.00"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -420,14 +403,14 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <name val="Liberation Serif;Times New Roman"/>
-      <family val="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="1"/>
     </font>
     <font>
@@ -517,7 +500,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -534,8 +517,24 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -672,7 +671,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.5"/>
@@ -741,6 +740,22 @@
         <v>15</v>
       </c>
     </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E2" s="1"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="6"/>
+      <c r="I2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="M2" s="8"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="6"/>
+      <c r="I3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="M3" s="8"/>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/Planilhas_importação/Importacao_unidades.xlsx
+++ b/Planilhas_importação/Importacao_unidades.xlsx
@@ -74,7 +74,8 @@
           <t xml:space="preserve">Obrigatório. Informe o status atual da unidade, utilizando uma das nomenclaturas abaixo:
 - DISPONIVEL
 - RESERVA_TECNICA
-- VENDIDO</t>
+- VENDIDO
+- DISTRATADO</t>
         </r>
       </text>
     </comment>
@@ -428,8 +429,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF34B3FB"/>
+        <bgColor rgb="FF00CCFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -442,7 +443,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="31">
+  <cellStyleXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -499,6 +500,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -538,7 +542,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="17">
+  <cellStyles count="18">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="15" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
@@ -556,7 +560,68 @@
     <cellStyle name="Normal" xfId="28"/>
     <cellStyle name="Título de tabela" xfId="29"/>
     <cellStyle name="Índice" xfId="30"/>
+    <cellStyle name="caption" xfId="31"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF34B3FB"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
